--- a/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_OS_detailed_results_0_95.xlsx
+++ b/EX1/Baseline_prediction_posteriors/LApredict/LaPredict_OS_detailed_results_0_95.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\LApredict\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB96F340-B207-4CE1-99D4-3D83407D2630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{133908F1-E1EA-46CD-97E4-9471A5D46BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31760" yWindow="11310" windowWidth="23660" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="valid" sheetId="1" r:id="rId1"/>
+    <sheet name="test" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">valid!$A$2:$M$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="17">
   <si>
     <t>Total Rows</t>
   </si>
@@ -86,20 +87,14 @@
     <t>recall fault-prone</t>
   </si>
   <si>
-    <t xml:space="preserve">AVG test </t>
-  </si>
-  <si>
     <t>AVG Valid</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -110,13 +105,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -165,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -176,7 +165,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -417,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q106"/>
+  <dimension ref="A1:Q104"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.21875" customWidth="1"/>
@@ -429,6 +419,7 @@
     <col min="8" max="8" width="21.5546875" customWidth="1"/>
     <col min="9" max="9" width="14.5546875" customWidth="1"/>
     <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
@@ -3982,15 +3973,15 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="N68">
-        <f t="shared" ref="N68:N101" si="6">H68/B68</f>
+        <f t="shared" ref="N68:N100" si="6">H68/B68</f>
         <v>6.5885797950219621E-2</v>
       </c>
       <c r="O68">
-        <f t="shared" ref="O68:O101" si="7">I68/C68</f>
+        <f t="shared" ref="O68:O100" si="7">I68/C68</f>
         <v>6.9565217391304349E-2</v>
       </c>
       <c r="P68">
-        <f t="shared" ref="P68:P101" si="8">J68/D68</f>
+        <f t="shared" ref="P68:P100" si="8">J68/D68</f>
         <v>1.9801980198019802E-2</v>
       </c>
     </row>
@@ -5215,776 +5206,654 @@
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>4552</v>
+        <v>1820</v>
       </c>
       <c r="B92">
-        <v>3707</v>
+        <v>1361</v>
       </c>
       <c r="C92">
-        <v>3506</v>
+        <v>1250</v>
       </c>
       <c r="D92">
-        <v>201</v>
+        <v>111</v>
       </c>
       <c r="E92">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="F92">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="G92">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H92">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="I92">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="J92">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K92">
-        <v>0.94594594594594594</v>
+        <v>0.92241379310344829</v>
       </c>
       <c r="L92">
-        <v>0.95402298850574707</v>
+        <v>0.95370370370370372</v>
       </c>
       <c r="M92">
-        <v>0.81818181818181823</v>
+        <v>0.5</v>
       </c>
       <c r="N92">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>7.861866274797942E-2</v>
       </c>
       <c r="O92">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>8.2400000000000001E-2</v>
       </c>
       <c r="P92">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>3.6036036036036036E-2</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93">
-        <v>4552</v>
+        <v>1820</v>
       </c>
       <c r="B93">
-        <v>3707</v>
+        <v>1361</v>
       </c>
       <c r="C93">
-        <v>3506</v>
+        <v>1267</v>
       </c>
       <c r="D93">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="E93">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="F93">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="G93">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H93">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="I93">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="J93">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K93">
-        <v>0.94594594594594594</v>
+        <v>0.99099099099099097</v>
       </c>
       <c r="L93">
-        <v>0.95402298850574707</v>
+        <v>0.99099099099099097</v>
       </c>
       <c r="M93">
-        <v>0.81818181818181823</v>
+        <v>0</v>
       </c>
       <c r="N93">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>8.0822924320352679E-2</v>
       </c>
       <c r="O93">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>8.6819258089976328E-2</v>
       </c>
       <c r="P93">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B94">
-        <v>3707</v>
+        <v>1365</v>
       </c>
       <c r="C94">
-        <v>3506</v>
+        <v>1268</v>
       </c>
       <c r="D94">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="E94">
-        <v>185</v>
+        <v>125</v>
       </c>
       <c r="F94">
-        <v>174</v>
+        <v>122</v>
       </c>
       <c r="G94">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H94">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="I94">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="J94">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K94">
-        <v>0.94594594594594594</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="L94">
-        <v>0.95402298850574707</v>
+        <v>0.95081967213114749</v>
       </c>
       <c r="M94">
-        <v>0.81818181818181823</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N94">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>8.6446886446886445E-2</v>
       </c>
       <c r="O94">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>9.1482649842271294E-2</v>
       </c>
       <c r="P94">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>2.0618556701030927E-2</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B95">
-        <v>3707</v>
+        <v>1356</v>
       </c>
       <c r="C95">
-        <v>3506</v>
+        <v>1254</v>
       </c>
       <c r="D95">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="E95">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="F95">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="G95">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H95">
-        <v>175</v>
+        <v>84</v>
       </c>
       <c r="I95">
-        <v>166</v>
+        <v>83</v>
       </c>
       <c r="J95">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K95">
-        <v>0.94594594594594594</v>
+        <v>0.9438202247191011</v>
       </c>
       <c r="L95">
-        <v>0.95402298850574707</v>
+        <v>0.96511627906976749</v>
       </c>
       <c r="M95">
-        <v>0.81818181818181823</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N95">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>6.1946902654867256E-2</v>
       </c>
       <c r="O95">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>6.6188197767145129E-2</v>
       </c>
       <c r="P95">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>9.8039215686274508E-3</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B96">
-        <v>3707</v>
+        <v>1346</v>
       </c>
       <c r="C96">
-        <v>3506</v>
+        <v>1253</v>
       </c>
       <c r="D96">
-        <v>201</v>
+        <v>93</v>
       </c>
       <c r="E96">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="F96">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="G96">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H96">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="I96">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="J96">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K96">
-        <v>0.94594594594594594</v>
+        <v>0.92372881355932202</v>
       </c>
       <c r="L96">
-        <v>0.95402298850574707</v>
+        <v>0.95575221238938057</v>
       </c>
       <c r="M96">
-        <v>0.81818181818181823</v>
+        <v>0.2</v>
       </c>
       <c r="N96">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>8.0980683506686482E-2</v>
       </c>
       <c r="O96">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>8.6193136472466084E-2</v>
       </c>
       <c r="P96">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>1.0752688172043012E-2</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B97">
-        <v>3707</v>
+        <v>1368</v>
       </c>
       <c r="C97">
-        <v>3506</v>
+        <v>1277</v>
       </c>
       <c r="D97">
-        <v>201</v>
+        <v>91</v>
       </c>
       <c r="E97">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="F97">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="G97">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H97">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="I97">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="J97">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K97">
-        <v>0.94594594594594594</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="L97">
-        <v>0.95402298850574707</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="M97">
-        <v>0.81818181818181823</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="N97">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>6.6520467836257313E-2</v>
       </c>
       <c r="O97">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>7.0477682067345337E-2</v>
       </c>
       <c r="P97">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>1.098901098901099E-2</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B98">
-        <v>3707</v>
+        <v>1382</v>
       </c>
       <c r="C98">
-        <v>3506</v>
+        <v>1268</v>
       </c>
       <c r="D98">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="E98">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="F98">
-        <v>174</v>
+        <v>105</v>
       </c>
       <c r="G98">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H98">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="I98">
-        <v>166</v>
+        <v>101</v>
       </c>
       <c r="J98">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K98">
-        <v>0.94594594594594594</v>
+        <v>0.95370370370370372</v>
       </c>
       <c r="L98">
-        <v>0.95402298850574707</v>
+        <v>0.96190476190476193</v>
       </c>
       <c r="M98">
-        <v>0.81818181818181823</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N98">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>7.4529667149059328E-2</v>
       </c>
       <c r="O98">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>7.9652996845425872E-2</v>
       </c>
       <c r="P98">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>1.7543859649122806E-2</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B99">
-        <v>3707</v>
+        <v>1369</v>
       </c>
       <c r="C99">
-        <v>3506</v>
+        <v>1271</v>
       </c>
       <c r="D99">
-        <v>201</v>
+        <v>98</v>
       </c>
       <c r="E99">
-        <v>185</v>
+        <v>111</v>
       </c>
       <c r="F99">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="G99">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H99">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="I99">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="J99">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K99">
-        <v>0.94594594594594594</v>
+        <v>0.97297297297297303</v>
       </c>
       <c r="L99">
-        <v>0.95402298850574707</v>
+        <v>0.98148148148148151</v>
       </c>
       <c r="M99">
-        <v>0.81818181818181823</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N99">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>7.8889700511322131E-2</v>
       </c>
       <c r="O99">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>8.3398898505114089E-2</v>
       </c>
       <c r="P99">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>2.0408163265306121E-2</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B100">
-        <v>3707</v>
+        <v>1392</v>
       </c>
       <c r="C100">
-        <v>3506</v>
+        <v>1283</v>
       </c>
       <c r="D100">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="E100">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="F100">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="G100">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H100">
-        <v>175</v>
+        <v>113</v>
       </c>
       <c r="I100">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="J100">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K100">
-        <v>0.94594594594594594</v>
+        <v>0.97413793103448276</v>
       </c>
       <c r="L100">
-        <v>0.95402298850574707</v>
+        <v>0.9910714285714286</v>
       </c>
       <c r="M100">
-        <v>0.81818181818181823</v>
+        <v>0.5</v>
       </c>
       <c r="N100">
         <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <v>8.1178160919540235E-2</v>
       </c>
       <c r="O100">
         <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <v>8.6515978176149644E-2</v>
       </c>
       <c r="P100">
         <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <v>1.834862385321101E-2</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101">
-        <v>4552</v>
+        <v>1820</v>
       </c>
       <c r="B101">
-        <v>3707</v>
+        <v>1358</v>
       </c>
       <c r="C101">
-        <v>3506</v>
+        <v>1272</v>
       </c>
       <c r="D101">
-        <v>201</v>
+        <v>86</v>
       </c>
       <c r="E101">
-        <v>185</v>
+        <v>122</v>
       </c>
       <c r="F101">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="G101">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H101">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="I101">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="J101">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K101">
-        <v>0.94594594594594594</v>
+        <v>0.95901639344262291</v>
       </c>
       <c r="L101">
-        <v>0.95402298850574707</v>
+        <v>0.95867768595041325</v>
       </c>
       <c r="M101">
-        <v>0.81818181818181823</v>
+        <v>1</v>
       </c>
       <c r="N101">
-        <f t="shared" si="6"/>
-        <v>4.7207984893444833E-2</v>
+        <f>H101/B101</f>
+        <v>8.6156111929307805E-2</v>
       </c>
       <c r="O101">
-        <f t="shared" si="7"/>
-        <v>4.7347404449515115E-2</v>
+        <f>I101/C101</f>
+        <v>9.1194968553459113E-2</v>
       </c>
       <c r="P101">
-        <f t="shared" si="8"/>
-        <v>4.4776119402985072E-2</v>
+        <f>J101/D101</f>
+        <v>1.1627906976744186E-2</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102">
-        <v>4552</v>
+        <v>1821</v>
       </c>
       <c r="B102">
-        <v>3707</v>
+        <v>1357</v>
       </c>
       <c r="C102">
-        <v>3506</v>
+        <v>1265</v>
       </c>
       <c r="D102">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="E102">
-        <v>185</v>
+        <v>115</v>
       </c>
       <c r="F102">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="G102">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H102">
-        <v>175</v>
+        <v>108</v>
       </c>
       <c r="I102">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="J102">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K102">
-        <v>0.94594594594594594</v>
+        <v>0.93913043478260871</v>
       </c>
       <c r="L102">
-        <v>0.95402298850574707</v>
+        <v>0.95495495495495497</v>
       </c>
       <c r="M102">
-        <v>0.81818181818181823</v>
+        <v>0.5</v>
       </c>
       <c r="N102">
-        <f>H102/B102</f>
-        <v>4.7207984893444833E-2</v>
+        <f t="shared" ref="N102" si="9">H102/B102</f>
+        <v>7.9587324981577001E-2</v>
       </c>
       <c r="O102">
-        <f>I102/C102</f>
-        <v>4.7347404449515115E-2</v>
+        <f t="shared" ref="O102" si="10">I102/C102</f>
+        <v>8.3794466403162057E-2</v>
       </c>
       <c r="P102">
-        <f>J102/D102</f>
-        <v>4.4776119402985072E-2</v>
+        <f t="shared" ref="P102" si="11">J102/D102</f>
+        <v>2.1739130434782608E-2</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A104">
-        <f t="shared" ref="A104:P104" si="9">AVERAGE(A92:A102)</f>
-        <v>4552</v>
-      </c>
-      <c r="B104">
-        <f t="shared" si="9"/>
-        <v>3707</v>
-      </c>
-      <c r="C104">
-        <f t="shared" si="9"/>
-        <v>3506</v>
-      </c>
-      <c r="D104">
-        <f t="shared" si="9"/>
-        <v>201</v>
-      </c>
-      <c r="E104">
-        <f t="shared" si="9"/>
-        <v>185</v>
-      </c>
-      <c r="F104">
-        <f t="shared" si="9"/>
-        <v>174</v>
-      </c>
-      <c r="G104">
-        <f t="shared" si="9"/>
-        <v>11</v>
-      </c>
-      <c r="H104">
-        <f t="shared" si="9"/>
-        <v>175</v>
-      </c>
-      <c r="I104">
-        <f t="shared" si="9"/>
-        <v>166</v>
-      </c>
-      <c r="J104">
-        <f t="shared" si="9"/>
-        <v>9</v>
-      </c>
-      <c r="K104">
-        <f t="shared" si="9"/>
-        <v>0.94594594594594572</v>
-      </c>
-      <c r="L104">
-        <f t="shared" si="9"/>
-        <v>0.95402298850574685</v>
-      </c>
-      <c r="M104">
-        <f t="shared" si="9"/>
-        <v>0.81818181818181823</v>
-      </c>
-      <c r="N104">
-        <f t="shared" si="9"/>
-        <v>4.720798489344484E-2</v>
-      </c>
-      <c r="O104">
-        <f t="shared" si="9"/>
-        <v>4.7347404449515122E-2</v>
-      </c>
-      <c r="P104">
-        <f t="shared" si="9"/>
-        <v>4.4776119402985086E-2</v>
+      <c r="A104" s="5">
+        <f>AVERAGE(A3:A102)</f>
+        <v>1820.54</v>
+      </c>
+      <c r="B104" s="5">
+        <f>AVERAGE(B3:B102)</f>
+        <v>1360.16</v>
+      </c>
+      <c r="C104" s="5">
+        <f>AVERAGE(C3:C102)</f>
+        <v>1261.19</v>
+      </c>
+      <c r="D104" s="5">
+        <f>AVERAGE(D3:D102)</f>
+        <v>98.97</v>
+      </c>
+      <c r="E104" s="5">
+        <f>AVERAGE(E3:E102)</f>
+        <v>105.36</v>
+      </c>
+      <c r="F104" s="5">
+        <f>AVERAGE(F3:F102)</f>
+        <v>102.48</v>
+      </c>
+      <c r="G104" s="5">
+        <f>AVERAGE(G3:G102)</f>
+        <v>2.88</v>
+      </c>
+      <c r="H104" s="5">
+        <f>AVERAGE(H3:H102)</f>
+        <v>100.64</v>
+      </c>
+      <c r="I104" s="5">
+        <f>AVERAGE(I3:I102)</f>
+        <v>99.17</v>
+      </c>
+      <c r="J104" s="5">
+        <f>AVERAGE(J3:J102)</f>
+        <v>1.47</v>
+      </c>
+      <c r="K104" s="4">
+        <f>AVERAGE(K3:K102)</f>
+        <v>0.95528150884213092</v>
+      </c>
+      <c r="L104" s="4">
+        <f>AVERAGE(L3:L102)</f>
+        <v>0.96781399982951333</v>
+      </c>
+      <c r="M104" s="4">
+        <f>AVERAGE(M3:M102)</f>
+        <v>0.53576190476190466</v>
+      </c>
+      <c r="N104" s="4">
+        <f>AVERAGE(N3:N102)</f>
+        <v>7.3985989616427564E-2</v>
+      </c>
+      <c r="O104" s="4">
+        <f>AVERAGE(O3:O102)</f>
+        <v>7.8612512218803193E-2</v>
+      </c>
+      <c r="P104" s="4">
+        <f>AVERAGE(P3:P102)</f>
+        <v>1.4763369070363859E-2</v>
       </c>
       <c r="Q104" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A105">
-        <f t="shared" ref="A105:P105" si="10">AVERAGE(A3:A91)</f>
-        <v>1820.5168539325844</v>
-      </c>
-      <c r="B105">
-        <f t="shared" si="10"/>
-        <v>1359.5617977528091</v>
-      </c>
-      <c r="C105">
-        <f t="shared" si="10"/>
-        <v>1260.5730337078651</v>
-      </c>
-      <c r="D105">
-        <f t="shared" si="10"/>
-        <v>98.988764044943821</v>
-      </c>
-      <c r="E105">
-        <f t="shared" si="10"/>
-        <v>104.57303370786516</v>
-      </c>
-      <c r="F105">
-        <f t="shared" si="10"/>
-        <v>101.75280898876404</v>
-      </c>
-      <c r="G105">
-        <f t="shared" si="10"/>
-        <v>2.8202247191011236</v>
-      </c>
-      <c r="H105">
-        <f t="shared" si="10"/>
-        <v>99.955056179775283</v>
-      </c>
-      <c r="I105">
-        <f t="shared" si="10"/>
-        <v>98.50561797752809</v>
-      </c>
-      <c r="J105">
-        <f t="shared" si="10"/>
-        <v>1.449438202247191</v>
-      </c>
-      <c r="K105">
-        <f t="shared" si="10"/>
-        <v>0.95590633929586966</v>
-      </c>
-      <c r="L105">
-        <f t="shared" si="10"/>
-        <v>0.96819728528933313</v>
-      </c>
-      <c r="M105">
-        <f t="shared" si="10"/>
-        <v>0.54168004280363813</v>
-      </c>
-      <c r="N105">
-        <f t="shared" si="10"/>
-        <v>7.3515971557740672E-2</v>
-      </c>
-      <c r="O105">
-        <f t="shared" si="10"/>
-        <v>7.8125089765818029E-2</v>
-      </c>
-      <c r="P105">
-        <f t="shared" si="10"/>
-        <v>1.4589539431353601E-2</v>
-      </c>
-      <c r="Q105" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="4">
-        <v>194801</v>
-      </c>
-      <c r="B106" s="4">
-        <v>147917</v>
-      </c>
-      <c r="C106" s="4">
-        <v>137699</v>
-      </c>
-      <c r="D106" s="4">
-        <v>10218</v>
-      </c>
-      <c r="E106" s="4">
-        <v>10557</v>
-      </c>
-      <c r="F106" s="4">
-        <v>10222</v>
-      </c>
-      <c r="G106" s="4">
-        <v>335</v>
-      </c>
-      <c r="H106" s="4">
-        <v>10076</v>
-      </c>
-      <c r="I106" s="4">
-        <v>9878</v>
-      </c>
-      <c r="J106" s="4">
-        <v>198</v>
-      </c>
-      <c r="K106" s="4">
-        <v>0.95443781377285208</v>
-      </c>
-      <c r="L106" s="4">
-        <v>0.96634709450205436</v>
-      </c>
-      <c r="M106" s="4">
-        <v>0.59104477611940298</v>
-      </c>
-      <c r="N106" s="4">
-        <v>0.59104477611940298</v>
-      </c>
-      <c r="O106" s="4">
-        <v>0.59104477611940298</v>
-      </c>
-      <c r="P106" s="4">
-        <v>0.59104477611940298</v>
-      </c>
-      <c r="Q106" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -5996,4 +5865,713 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A591EFC0-13CC-4F1F-A4BE-309A2B9408AD}">
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>4552</v>
+      </c>
+      <c r="B2">
+        <v>3707</v>
+      </c>
+      <c r="C2">
+        <v>3506</v>
+      </c>
+      <c r="D2">
+        <v>201</v>
+      </c>
+      <c r="E2">
+        <v>185</v>
+      </c>
+      <c r="F2">
+        <v>174</v>
+      </c>
+      <c r="G2">
+        <v>11</v>
+      </c>
+      <c r="H2">
+        <v>175</v>
+      </c>
+      <c r="I2">
+        <v>166</v>
+      </c>
+      <c r="J2">
+        <v>9</v>
+      </c>
+      <c r="K2">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L2">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M2">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N2">
+        <f t="shared" ref="N2:P12" si="0">H2/B2</f>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O2">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P2">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4552</v>
+      </c>
+      <c r="B3">
+        <v>3707</v>
+      </c>
+      <c r="C3">
+        <v>3506</v>
+      </c>
+      <c r="D3">
+        <v>201</v>
+      </c>
+      <c r="E3">
+        <v>185</v>
+      </c>
+      <c r="F3">
+        <v>174</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>175</v>
+      </c>
+      <c r="I3">
+        <v>166</v>
+      </c>
+      <c r="J3">
+        <v>9</v>
+      </c>
+      <c r="K3">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L3">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M3">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N3">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O3">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P3">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>4552</v>
+      </c>
+      <c r="B4">
+        <v>3707</v>
+      </c>
+      <c r="C4">
+        <v>3506</v>
+      </c>
+      <c r="D4">
+        <v>201</v>
+      </c>
+      <c r="E4">
+        <v>185</v>
+      </c>
+      <c r="F4">
+        <v>174</v>
+      </c>
+      <c r="G4">
+        <v>11</v>
+      </c>
+      <c r="H4">
+        <v>175</v>
+      </c>
+      <c r="I4">
+        <v>166</v>
+      </c>
+      <c r="J4">
+        <v>9</v>
+      </c>
+      <c r="K4">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L4">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M4">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P4">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4552</v>
+      </c>
+      <c r="B5">
+        <v>3707</v>
+      </c>
+      <c r="C5">
+        <v>3506</v>
+      </c>
+      <c r="D5">
+        <v>201</v>
+      </c>
+      <c r="E5">
+        <v>185</v>
+      </c>
+      <c r="F5">
+        <v>174</v>
+      </c>
+      <c r="G5">
+        <v>11</v>
+      </c>
+      <c r="H5">
+        <v>175</v>
+      </c>
+      <c r="I5">
+        <v>166</v>
+      </c>
+      <c r="J5">
+        <v>9</v>
+      </c>
+      <c r="K5">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L5">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M5">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P5">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>4552</v>
+      </c>
+      <c r="B6">
+        <v>3707</v>
+      </c>
+      <c r="C6">
+        <v>3506</v>
+      </c>
+      <c r="D6">
+        <v>201</v>
+      </c>
+      <c r="E6">
+        <v>185</v>
+      </c>
+      <c r="F6">
+        <v>174</v>
+      </c>
+      <c r="G6">
+        <v>11</v>
+      </c>
+      <c r="H6">
+        <v>175</v>
+      </c>
+      <c r="I6">
+        <v>166</v>
+      </c>
+      <c r="J6">
+        <v>9</v>
+      </c>
+      <c r="K6">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L6">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M6">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>4552</v>
+      </c>
+      <c r="B7">
+        <v>3707</v>
+      </c>
+      <c r="C7">
+        <v>3506</v>
+      </c>
+      <c r="D7">
+        <v>201</v>
+      </c>
+      <c r="E7">
+        <v>185</v>
+      </c>
+      <c r="F7">
+        <v>174</v>
+      </c>
+      <c r="G7">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>175</v>
+      </c>
+      <c r="I7">
+        <v>166</v>
+      </c>
+      <c r="J7">
+        <v>9</v>
+      </c>
+      <c r="K7">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L7">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M7">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>4552</v>
+      </c>
+      <c r="B8">
+        <v>3707</v>
+      </c>
+      <c r="C8">
+        <v>3506</v>
+      </c>
+      <c r="D8">
+        <v>201</v>
+      </c>
+      <c r="E8">
+        <v>185</v>
+      </c>
+      <c r="F8">
+        <v>174</v>
+      </c>
+      <c r="G8">
+        <v>11</v>
+      </c>
+      <c r="H8">
+        <v>175</v>
+      </c>
+      <c r="I8">
+        <v>166</v>
+      </c>
+      <c r="J8">
+        <v>9</v>
+      </c>
+      <c r="K8">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L8">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M8">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4552</v>
+      </c>
+      <c r="B9">
+        <v>3707</v>
+      </c>
+      <c r="C9">
+        <v>3506</v>
+      </c>
+      <c r="D9">
+        <v>201</v>
+      </c>
+      <c r="E9">
+        <v>185</v>
+      </c>
+      <c r="F9">
+        <v>174</v>
+      </c>
+      <c r="G9">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>175</v>
+      </c>
+      <c r="I9">
+        <v>166</v>
+      </c>
+      <c r="J9">
+        <v>9</v>
+      </c>
+      <c r="K9">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L9">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M9">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>4552</v>
+      </c>
+      <c r="B10">
+        <v>3707</v>
+      </c>
+      <c r="C10">
+        <v>3506</v>
+      </c>
+      <c r="D10">
+        <v>201</v>
+      </c>
+      <c r="E10">
+        <v>185</v>
+      </c>
+      <c r="F10">
+        <v>174</v>
+      </c>
+      <c r="G10">
+        <v>11</v>
+      </c>
+      <c r="H10">
+        <v>175</v>
+      </c>
+      <c r="I10">
+        <v>166</v>
+      </c>
+      <c r="J10">
+        <v>9</v>
+      </c>
+      <c r="K10">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L10">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M10">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>4552</v>
+      </c>
+      <c r="B11">
+        <v>3707</v>
+      </c>
+      <c r="C11">
+        <v>3506</v>
+      </c>
+      <c r="D11">
+        <v>201</v>
+      </c>
+      <c r="E11">
+        <v>185</v>
+      </c>
+      <c r="F11">
+        <v>174</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+      <c r="H11">
+        <v>175</v>
+      </c>
+      <c r="I11">
+        <v>166</v>
+      </c>
+      <c r="J11">
+        <v>9</v>
+      </c>
+      <c r="K11">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L11">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M11">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>4552</v>
+      </c>
+      <c r="B12">
+        <v>3707</v>
+      </c>
+      <c r="C12">
+        <v>3506</v>
+      </c>
+      <c r="D12">
+        <v>201</v>
+      </c>
+      <c r="E12">
+        <v>185</v>
+      </c>
+      <c r="F12">
+        <v>174</v>
+      </c>
+      <c r="G12">
+        <v>11</v>
+      </c>
+      <c r="H12">
+        <v>175</v>
+      </c>
+      <c r="I12">
+        <v>166</v>
+      </c>
+      <c r="J12">
+        <v>9</v>
+      </c>
+      <c r="K12">
+        <v>0.94594594594594594</v>
+      </c>
+      <c r="L12">
+        <v>0.95402298850574707</v>
+      </c>
+      <c r="M12">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N12">
+        <f>H12/B12</f>
+        <v>4.7207984893444833E-2</v>
+      </c>
+      <c r="O12">
+        <f>I12/C12</f>
+        <v>4.7347404449515115E-2</v>
+      </c>
+      <c r="P12">
+        <f>J12/D12</f>
+        <v>4.4776119402985072E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <f>AVERAGE(A2:A12)</f>
+        <v>4552</v>
+      </c>
+      <c r="B14">
+        <f t="shared" ref="B14:P14" si="1">AVERAGE(B2:B12)</f>
+        <v>3707</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="1"/>
+        <v>3506</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="1"/>
+        <v>201</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>185</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>174</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>175</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="1"/>
+        <v>166</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="1"/>
+        <v>0.94594594594594572</v>
+      </c>
+      <c r="L14" s="4">
+        <f t="shared" si="1"/>
+        <v>0.95402298850574685</v>
+      </c>
+      <c r="M14" s="4">
+        <f t="shared" si="1"/>
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="N14" s="4">
+        <f t="shared" si="1"/>
+        <v>4.720798489344484E-2</v>
+      </c>
+      <c r="O14" s="4">
+        <f t="shared" si="1"/>
+        <v>4.7347404449515122E-2</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="1"/>
+        <v>4.4776119402985086E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>